--- a/tests/testthat/fixtures/praemienregionen.xlsx
+++ b/tests/testthat/fixtures/praemienregionen.xlsx
@@ -7,8 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A_COM" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Informationen" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MUT" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A_COM" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C_POP" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,13 +416,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Prämienregionen 2026</t>
+          <t>Prämienregionen gültig ab 01.01.2026 bis 31.12.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Release: release-2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BFS-Gemeindenummer = Primärschlüssel für die Region</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Die Kantone mit einer einzigen Region (0) sind: AG, AI, AR, BS, GE, GL, JU, NE, NW, OW, SO, SZ, TG, UR, ZG</t>
         </is>
       </c>
     </row>
@@ -435,360 +460,413 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Mutationen 2023-2024 (BFS-Nr.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Gemeinden mit geänderter Region</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BFS-Nr.
+No OFS</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Gemeinde alt
+Commune ancienne</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Region alt
+Région ancienne</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="n">
+        <v>767</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Reutigen</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Prämienregionen gültig ab 1.1.2026</t>
+          <t>A_COM (v.01.08.2025)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Quelle: BAG</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Kanton</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Region</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>BFS-Nr.</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Gemeinde</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Bezirk</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>PLZ</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Ortschaft</t>
+          <t>Eine Gemeinde kann mehrere PLZ umfassen und eine PLZ kann in mehreren Gemeinden liegen.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>BFS-Nr.
+No OFS</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kanton
+Canton</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Gemeinde
+Commune</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Region
+Région</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Bezirk
+District</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>PLZ
+NPA</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Ort
+Localité</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>ZH</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Aeugst am Albis</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>Affoltern</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>8914</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="F6" t="n">
+        <v>8914</v>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>Aeugst am Albis</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>ZH</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Aeugst am Albis</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Affoltern</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>8914</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Aeugstertal</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ZH</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>Affoltern am Albis</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>Affoltern</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>8910</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Affoltern am Albis</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="F8" t="n">
+        <v>8909</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Zwillikon</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>261</v>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>ZH</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Zürich</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>Zürich</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>8001</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="F9" t="n">
+        <v>8001</v>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>Zürich</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>ZH</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Zürich</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Zürich</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>8002</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Zürich</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="n">
+        <v>351</v>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>351</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Bern</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>Bern-Mittelland</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>3011</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="F10" t="n">
+        <v>3011</v>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>Bern</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="n">
+        <v>999</v>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>999</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Teilgemeinde</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>Bern-Mittelland</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>3999</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="F11" t="n">
+        <v>3999</v>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>Ort A</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="n">
+        <v>999</v>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>999</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Teilgemeinde</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>Bern-Mittelland</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>3998</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="F12" t="n">
+        <v>3998</v>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>Ort B</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6621</v>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>GE</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>6621</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Genève</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>Genève</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>1204</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
+      <c r="F13" t="n">
+        <v>1204</v>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>Genève</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Fussnote: verbindlich ist die Verordnung</t>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>BFS-Nr.
+No OFS</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kanton
+Canton</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Gemeinde
+Commune</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Region
+Région</t>
         </is>
       </c>
     </row>
